--- a/resources/templates/standard/F2100-02.xlsx
+++ b/resources/templates/standard/F2100-02.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="49">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <r>
       <t xml:space="preserve">사내 자격 인증 카드
@@ -1094,12 +1097,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.15" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -1126,7 +1131,7 @@
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE1" s="2"/>
       <c r="AF1" s="2"/>
@@ -1375,7 +1380,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -1384,7 +1389,7 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
@@ -1404,7 +1409,7 @@
       <c r="AB5" s="5"/>
       <c r="AC5" s="5"/>
       <c r="AD5" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE5" s="6"/>
       <c r="AF5" s="6"/>
@@ -1413,7 +1418,7 @@
       <c r="AI5" s="7"/>
       <c r="AJ5" s="7"/>
       <c r="AK5" s="8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL5" s="8"/>
       <c r="AM5" s="8"/>
@@ -1429,7 +1434,7 @@
       <c r="AW5" s="8"/>
       <c r="AX5" s="3"/>
       <c r="AY5" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ5" s="9"/>
       <c r="BA5" s="9"/>
@@ -1440,7 +1445,7 @@
       <c r="BF5" s="10"/>
       <c r="BG5" s="10"/>
       <c r="BH5" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BI5" s="9"/>
       <c r="BJ5" s="9"/>
@@ -1455,7 +1460,7 @@
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
@@ -1464,7 +1469,7 @@
       <c r="J6" s="12"/>
       <c r="K6" s="12"/>
       <c r="L6" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6" s="13"/>
       <c r="N6" s="13"/>
@@ -1472,7 +1477,7 @@
       <c r="P6" s="13"/>
       <c r="Q6" s="13"/>
       <c r="R6" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S6" s="14"/>
       <c r="T6" s="14"/>
@@ -1486,7 +1491,7 @@
       <c r="AB6" s="5"/>
       <c r="AC6" s="5"/>
       <c r="AD6" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE6" s="11"/>
       <c r="AF6" s="11"/>
@@ -1495,7 +1500,7 @@
       <c r="AI6" s="12"/>
       <c r="AJ6" s="12"/>
       <c r="AK6" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL6" s="13"/>
       <c r="AM6" s="13"/>
@@ -1503,7 +1508,7 @@
       <c r="AO6" s="13"/>
       <c r="AP6" s="13"/>
       <c r="AQ6" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR6" s="14"/>
       <c r="AS6" s="14"/>
@@ -1524,7 +1529,7 @@
       <c r="BF6" s="10"/>
       <c r="BG6" s="10"/>
       <c r="BH6" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BI6" s="9"/>
       <c r="BJ6" s="9"/>
@@ -1539,7 +1544,7 @@
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
@@ -1548,7 +1553,7 @@
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
       <c r="L7" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
@@ -1571,7 +1576,7 @@
       <c r="AB7" s="5"/>
       <c r="AC7" s="5"/>
       <c r="AD7" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE7" s="11"/>
       <c r="AF7" s="11"/>
@@ -1580,7 +1585,7 @@
       <c r="AI7" s="12"/>
       <c r="AJ7" s="12"/>
       <c r="AK7" s="15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL7" s="15"/>
       <c r="AM7" s="15"/>
@@ -1610,7 +1615,7 @@
       <c r="BF7" s="10"/>
       <c r="BG7" s="10"/>
       <c r="BH7" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BI7" s="9"/>
       <c r="BJ7" s="9"/>
@@ -1625,7 +1630,7 @@
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
@@ -1634,7 +1639,7 @@
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
       <c r="L8" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
@@ -1657,7 +1662,7 @@
       <c r="AB8" s="5"/>
       <c r="AC8" s="5"/>
       <c r="AD8" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE8" s="16"/>
       <c r="AF8" s="16"/>
@@ -1702,7 +1707,7 @@
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
@@ -1711,7 +1716,7 @@
       <c r="J9" s="19"/>
       <c r="K9" s="19"/>
       <c r="L9" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
@@ -1731,7 +1736,7 @@
       <c r="AB9" s="5"/>
       <c r="AC9" s="5"/>
       <c r="AD9" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE9" s="11"/>
       <c r="AF9" s="11"/>
@@ -1740,7 +1745,7 @@
       <c r="AI9" s="20"/>
       <c r="AJ9" s="20"/>
       <c r="AK9" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL9" s="13"/>
       <c r="AM9" s="13"/>
@@ -1788,7 +1793,7 @@
       <c r="J10" s="19"/>
       <c r="K10" s="19"/>
       <c r="L10" s="21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M10" s="21"/>
       <c r="N10" s="21"/>
@@ -1796,7 +1801,7 @@
       <c r="P10" s="21"/>
       <c r="Q10" s="21"/>
       <c r="R10" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S10" s="22"/>
       <c r="T10" s="22"/>
@@ -1810,7 +1815,7 @@
       <c r="AB10" s="5"/>
       <c r="AC10" s="5"/>
       <c r="AD10" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE10" s="23"/>
       <c r="AF10" s="23"/>
@@ -1851,7 +1856,7 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -1861,12 +1866,12 @@
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J11" s="25"/>
       <c r="K11" s="25"/>
       <c r="L11" s="26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M11" s="27"/>
       <c r="N11" s="27"/>
@@ -1882,7 +1887,7 @@
       <c r="X11" s="27"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA11" s="8"/>
       <c r="AB11" s="8"/>
@@ -1892,15 +1897,15 @@
       <c r="AF11" s="8"/>
       <c r="AG11" s="8"/>
       <c r="AH11" s="25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI11" s="25"/>
       <c r="AJ11" s="25"/>
       <c r="AK11" s="28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL11" s="29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM11" s="29"/>
       <c r="AN11" s="29"/>
@@ -1933,11 +1938,11 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A12" s="30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12" s="31"/>
       <c r="E12" s="31"/>
@@ -1945,7 +1950,7 @@
       <c r="G12" s="31"/>
       <c r="H12" s="31"/>
       <c r="I12" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J12" s="32"/>
       <c r="K12" s="33"/>
@@ -1964,11 +1969,11 @@
       <c r="X12" s="27"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA12" s="34"/>
       <c r="AB12" s="31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC12" s="31"/>
       <c r="AD12" s="31"/>
@@ -1976,7 +1981,7 @@
       <c r="AF12" s="31"/>
       <c r="AG12" s="31"/>
       <c r="AH12" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI12" s="32"/>
       <c r="AJ12" s="33"/>
@@ -2015,7 +2020,7 @@
       <c r="A13" s="30"/>
       <c r="B13" s="30"/>
       <c r="C13" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13" s="35"/>
       <c r="E13" s="35"/>
@@ -2023,17 +2028,17 @@
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
       <c r="I13" s="36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J13" s="36"/>
       <c r="K13" s="37"/>
       <c r="L13" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P13" s="14"/>
       <c r="Q13" s="14"/>
@@ -2042,7 +2047,7 @@
       <c r="T13" s="14"/>
       <c r="U13" s="14"/>
       <c r="V13" s="14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W13" s="14"/>
       <c r="X13" s="14"/>
@@ -2050,7 +2055,7 @@
       <c r="Z13" s="34"/>
       <c r="AA13" s="34"/>
       <c r="AB13" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC13" s="35"/>
       <c r="AD13" s="35"/>
@@ -2058,7 +2063,7 @@
       <c r="AF13" s="35"/>
       <c r="AG13" s="35"/>
       <c r="AH13" s="36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI13" s="36"/>
       <c r="AJ13" s="37"/>
@@ -2095,11 +2100,11 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A14" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14" s="30"/>
       <c r="C14" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
@@ -2107,7 +2112,7 @@
       <c r="G14" s="31"/>
       <c r="H14" s="31"/>
       <c r="I14" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J14" s="32"/>
       <c r="K14" s="33"/>
@@ -2126,11 +2131,11 @@
       <c r="X14" s="40"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA14" s="41"/>
       <c r="AB14" s="31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AC14" s="31"/>
       <c r="AD14" s="31"/>
@@ -2138,7 +2143,7 @@
       <c r="AF14" s="31"/>
       <c r="AG14" s="31"/>
       <c r="AH14" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI14" s="32"/>
       <c r="AJ14" s="33"/>
@@ -2177,7 +2182,7 @@
       <c r="A15" s="30"/>
       <c r="B15" s="30"/>
       <c r="C15" s="45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" s="45"/>
       <c r="E15" s="45"/>
@@ -2185,7 +2190,7 @@
       <c r="G15" s="45"/>
       <c r="H15" s="45"/>
       <c r="I15" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J15" s="46"/>
       <c r="K15" s="47"/>
@@ -2206,7 +2211,7 @@
       <c r="Z15" s="41"/>
       <c r="AA15" s="41"/>
       <c r="AB15" s="49" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC15" s="49"/>
       <c r="AD15" s="49"/>
@@ -2214,7 +2219,7 @@
       <c r="AF15" s="49"/>
       <c r="AG15" s="49"/>
       <c r="AH15" s="50" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AI15" s="50"/>
       <c r="AJ15" s="50"/>
@@ -2253,7 +2258,7 @@
       <c r="A16" s="30"/>
       <c r="B16" s="30"/>
       <c r="C16" s="35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="35"/>
       <c r="E16" s="35"/>
@@ -2261,7 +2266,7 @@
       <c r="G16" s="35"/>
       <c r="H16" s="35"/>
       <c r="I16" s="36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J16" s="36"/>
       <c r="K16" s="37"/>
@@ -2280,14 +2285,14 @@
       <c r="X16" s="40"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA16" s="8"/>
       <c r="AB16" s="8"/>
       <c r="AC16" s="8"/>
       <c r="AD16" s="8"/>
       <c r="AE16" s="25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF16" s="25"/>
       <c r="AG16" s="25"/>
@@ -2303,7 +2308,7 @@
       <c r="AQ16" s="25"/>
       <c r="AR16" s="25"/>
       <c r="AS16" s="52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AT16" s="52"/>
       <c r="AU16" s="52"/>
@@ -2329,11 +2334,11 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A17" s="30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="30"/>
       <c r="C17" s="31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="31"/>
       <c r="E17" s="31"/>
@@ -2341,7 +2346,7 @@
       <c r="G17" s="31"/>
       <c r="H17" s="31"/>
       <c r="I17" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J17" s="32"/>
       <c r="K17" s="33"/>
@@ -2405,7 +2410,7 @@
       <c r="A18" s="30"/>
       <c r="B18" s="30"/>
       <c r="C18" s="45" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18" s="45"/>
       <c r="E18" s="45"/>
@@ -2413,7 +2418,7 @@
       <c r="G18" s="45"/>
       <c r="H18" s="45"/>
       <c r="I18" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J18" s="46"/>
       <c r="K18" s="47"/>
@@ -2477,7 +2482,7 @@
       <c r="A19" s="30"/>
       <c r="B19" s="30"/>
       <c r="C19" s="45" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D19" s="45"/>
       <c r="E19" s="45"/>
@@ -2485,7 +2490,7 @@
       <c r="G19" s="45"/>
       <c r="H19" s="45"/>
       <c r="I19" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J19" s="46"/>
       <c r="K19" s="47"/>
@@ -2549,7 +2554,7 @@
       <c r="A20" s="30"/>
       <c r="B20" s="30"/>
       <c r="C20" s="45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D20" s="45"/>
       <c r="E20" s="45"/>
@@ -2557,7 +2562,7 @@
       <c r="G20" s="45"/>
       <c r="H20" s="45"/>
       <c r="I20" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J20" s="46"/>
       <c r="K20" s="47"/>
@@ -2621,7 +2626,7 @@
       <c r="A21" s="30"/>
       <c r="B21" s="30"/>
       <c r="C21" s="45" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D21" s="45"/>
       <c r="E21" s="45"/>
@@ -2629,7 +2634,7 @@
       <c r="G21" s="45"/>
       <c r="H21" s="45"/>
       <c r="I21" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J21" s="46"/>
       <c r="K21" s="47"/>
@@ -2693,7 +2698,7 @@
       <c r="A22" s="30"/>
       <c r="B22" s="30"/>
       <c r="C22" s="45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D22" s="45"/>
       <c r="E22" s="45"/>
@@ -2701,7 +2706,7 @@
       <c r="G22" s="45"/>
       <c r="H22" s="45"/>
       <c r="I22" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J22" s="46"/>
       <c r="K22" s="47"/>
@@ -2765,7 +2770,7 @@
       <c r="A23" s="30"/>
       <c r="B23" s="30"/>
       <c r="C23" s="45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D23" s="45"/>
       <c r="E23" s="45"/>
@@ -2773,7 +2778,7 @@
       <c r="G23" s="45"/>
       <c r="H23" s="45"/>
       <c r="I23" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J23" s="46"/>
       <c r="K23" s="47"/>
@@ -2837,7 +2842,7 @@
       <c r="A24" s="30"/>
       <c r="B24" s="30"/>
       <c r="C24" s="45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D24" s="45"/>
       <c r="E24" s="45"/>
@@ -2845,7 +2850,7 @@
       <c r="G24" s="45"/>
       <c r="H24" s="45"/>
       <c r="I24" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J24" s="46"/>
       <c r="K24" s="47"/>
@@ -2909,7 +2914,7 @@
       <c r="A25" s="30"/>
       <c r="B25" s="30"/>
       <c r="C25" s="45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D25" s="45"/>
       <c r="E25" s="45"/>
@@ -2917,7 +2922,7 @@
       <c r="G25" s="45"/>
       <c r="H25" s="45"/>
       <c r="I25" s="46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J25" s="46"/>
       <c r="K25" s="47"/>
